--- a/samples/수주취합/고객사G_발주서.xlsx
+++ b/samples/수주취합/고객사G_발주서.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="51">
   <si>
     <t>운영단위</t>
   </si>
@@ -719,11 +719,11 @@
       <c r="T2" t="s">
         <v>45</v>
       </c>
-      <c r="U2" t="s">
-        <v>39</v>
-      </c>
-      <c r="V2" t="s">
-        <v>39</v>
+      <c r="U2">
+        <v>7700</v>
+      </c>
+      <c r="V2">
+        <v>1540000</v>
       </c>
       <c r="W2" t="s">
         <v>39</v>
@@ -820,11 +820,11 @@
       <c r="T3" t="s">
         <v>45</v>
       </c>
-      <c r="U3" t="s">
-        <v>39</v>
-      </c>
-      <c r="V3" t="s">
-        <v>39</v>
+      <c r="U3">
+        <v>7900</v>
+      </c>
+      <c r="V3">
+        <v>632000</v>
       </c>
       <c r="W3" t="s">
         <v>39</v>
